--- a/tame_output/ON/bt/strategyON_20230808.xlsx
+++ b/tame_output/ON/bt/strategyON_20230808.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -610,11 +610,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.9%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-06</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.9%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1682"/>
+  <dimension ref="A1:G1683"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40196,7 +40196,7 @@
         <v>45144</v>
       </c>
       <c r="B1682" t="n">
-        <v>2.87792292593593</v>
+        <v>2.877218618201276</v>
       </c>
       <c r="C1682" t="n">
         <v>2.995226367051653</v>
@@ -40212,6 +40212,29 @@
       </c>
       <c r="G1682" t="n">
         <v>4.296842531842766</v>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" s="2" t="n">
+        <v>45145</v>
+      </c>
+      <c r="B1683" t="n">
+        <v>2.878552858630647</v>
+      </c>
+      <c r="C1683" t="n">
+        <v>2.997187714580352</v>
+      </c>
+      <c r="D1683" t="n">
+        <v>1.541189140412542</v>
+      </c>
+      <c r="E1683" t="n">
+        <v>3.613306946431622</v>
+      </c>
+      <c r="F1683" t="n">
+        <v>2.170065335310567</v>
+      </c>
+      <c r="G1683" t="n">
+        <v>4.299226915766694</v>
       </c>
     </row>
   </sheetData>
